--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484589_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484589_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6862</v>
+        <v>2.4499</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8423</v>
+        <v>1.705</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8439</v>
+        <v>0.7448</v>
       </c>
       <c r="G2" t="n">
         <v>2.3509</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7401</v>
+        <v>0.5038</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6026</v>
+        <v>0.4653</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1375</v>
+        <v>0.0384</v>
       </c>
       <c r="V2" t="n">
         <v>1.0613</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>M. GONZALEZ MAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4874</v>
+        <v>0.5622</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2607</v>
+        <v>1.1661</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7481</v>
+        <v>-0.6039</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2199</v>
+        <v>0.5944</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7134</v>
+        <v>-0.457</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5065</v>
+        <v>1.0514</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6076</v>
+        <v>1.982</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5077</v>
+        <v>0.065</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1154</v>
+        <v>1.917</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6122</v>
+        <v>-1.3876</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2211</v>
+        <v>-0.522</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6089</v>
+        <v>-0.8656</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9312</v>
+        <v>-0.0322</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3469</v>
+        <v>0.1003</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5843</v>
+        <v>-0.1325</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5068</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ MAS</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2405</v>
+        <v>0.2892</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9187</v>
+        <v>-0.2607</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6782</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5944</v>
+        <v>-1.2199</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.457</v>
+        <v>-0.7134</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0514</v>
+        <v>-0.5065</v>
       </c>
       <c r="J5" t="n">
-        <v>1.982</v>
+        <v>-0.6076</v>
       </c>
       <c r="K5" t="n">
-        <v>0.065</v>
+        <v>0.5077</v>
       </c>
       <c r="L5" t="n">
-        <v>1.917</v>
+        <v>-1.1154</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3876</v>
+        <v>-0.6122</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.522</v>
+        <v>-1.2211</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8656</v>
+        <v>0.6089</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3539</v>
+        <v>0.733</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1471</v>
+        <v>0.3469</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2069</v>
+        <v>0.3861</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5068</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5068</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2021</v>
+        <v>0.2511</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5986</v>
+        <v>-0.253</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3965</v>
+        <v>0.5042</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3913</v>
+        <v>-0.2576</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4261</v>
+        <v>1.2843</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8175</v>
+        <v>-1.5419</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0141</v>
+        <v>0.747</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9721</v>
+        <v>1.9041</v>
       </c>
       <c r="L6" t="n">
-        <v>2.042</v>
+        <v>-1.157</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6228</v>
+        <v>-1.0047</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3982</v>
+        <v>-0.6198</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2246</v>
+        <v>-0.3849</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9352</v>
+        <v>0.2705</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5008</v>
+        <v>0.2278</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5655</v>
+        <v>0.0428</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.0407</v>
+        <v>-0.3115</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.0407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1962</v>
+        <v>0.1333</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1089</v>
+        <v>0.9716</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9126</v>
+        <v>-0.8383</v>
       </c>
       <c r="G7" t="n">
         <v>0.7208</v>
@@ -1000,13 +1000,13 @@
         <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7087</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9698</v>
+        <v>0.8326</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2612</v>
+        <v>-0.1869</v>
       </c>
       <c r="V7" t="n">
         <v>0.9658</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2074</v>
+        <v>-0.248</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.885</v>
+        <v>2.9255</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6776</v>
+        <v>-3.1735</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2576</v>
+        <v>1.3913</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2843</v>
+        <v>-0.4261</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5419</v>
+        <v>1.8175</v>
       </c>
       <c r="J8" t="n">
-        <v>0.747</v>
+        <v>3.0141</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9041</v>
+        <v>0.9721</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.157</v>
+        <v>2.042</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0047</v>
+        <v>-1.6228</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6198</v>
+        <v>-1.3982</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3849</v>
+        <v>-0.2246</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.188</v>
+        <v>0.4851</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4042</v>
+        <v>0.8277</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2162</v>
+        <v>-0.3426</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3115</v>
+        <v>-3.0407</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.0407</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3973</v>
+        <v>-0.9518</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8195</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5779</v>
+        <v>-0.3797</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2362</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4727</v>
+        <v>-0.0272</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2187</v>
+        <v>0.4661</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6914</v>
+        <v>-0.4932</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3219</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5875</v>
+        <v>-1.4437</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1946</v>
+        <v>-2.1935</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.7821</v>
+        <v>0.7498</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9677</v>
+        <v>-2.9798</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4328</v>
+        <v>-1.5117</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4651</v>
+        <v>-1.4681</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7279</v>
+        <v>-1.583</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2693</v>
+        <v>-0.4676</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4586</v>
+        <v>-1.1154</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7602</v>
+        <v>-1.3968</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8365</v>
+        <v>-1.044</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.9237</v>
+        <v>-0.3528</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1991</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2745</v>
+        <v>0.3203</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6946</v>
+        <v>0.3058</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4201</v>
+        <v>0.0145</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.1125</v>
+        <v>0.1163</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.8009</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5941</v>
+        <v>-1.5735</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6359</v>
+        <v>3.2086</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.23</v>
+        <v>-4.7821</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8659</v>
+        <v>0.9677</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3721</v>
+        <v>1.4328</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4937</v>
+        <v>-0.4651</v>
       </c>
       <c r="J11" t="n">
-        <v>0.105</v>
+        <v>3.7279</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0217</v>
+        <v>2.2693</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0833</v>
+        <v>1.4586</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9709</v>
+        <v>-2.7602</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3938</v>
+        <v>-0.8365</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-1.9237</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.2885</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5309</v>
+        <v>0.7085</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0078</v>
+        <v>-0.4201</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.267</v>
+        <v>-4.1125</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1911</v>
+        <v>-2.0227</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8665</v>
+        <v>0.3064</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6755</v>
+        <v>-2.3291</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9798</v>
+        <v>-0.8659</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5117</v>
+        <v>-0.3721</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4681</v>
+        <v>-0.4937</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.583</v>
+        <v>0.105</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4676</v>
+        <v>0.0217</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1154</v>
+        <v>0.0833</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3968</v>
+        <v>-0.9709</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.044</v>
+        <v>-0.3938</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3528</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4271</v>
+        <v>0.1101</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3673</v>
+        <v>0.2014</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0598</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1163</v>
+        <v>-1.267</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1163</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5079</v>
+        <v>-7.5683</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5228</v>
+        <v>-5.5088</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9851</v>
+        <v>-2.0594</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4666</v>
@@ -1468,13 +1468,13 @@
         <v>2.5656</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1594</v>
+        <v>1.099</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6207</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5387</v>
+        <v>0.4643</v>
       </c>
       <c r="V13" t="n">
         <v>-3.3523</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.0227</v>
+        <v>-9.472099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.594699999999998</v>
+        <v>2.1453</v>
       </c>
       <c r="F14" t="n">
         <v>-11.6173</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3507</v>
+        <v>-0.3506999999999996</v>
       </c>
       <c r="H14" t="n">
         <v>2.2135</v>
@@ -1546,13 +1546,13 @@
         <v>17.4096</v>
       </c>
       <c r="S14" t="n">
-        <v>3.846200000000001</v>
+        <v>4.3966</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5664</v>
+        <v>5.117</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7203999999999999</v>
+        <v>-0.7205000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-10.7693</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2995</v>
+        <v>3.5311</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6877</v>
+        <v>3.2604</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6117</v>
+        <v>0.2707</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7002</v>
+        <v>-0.3279</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4372</v>
+        <v>-0.9015</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2631</v>
+        <v>0.5736</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4418</v>
+        <v>1.527</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1918</v>
+        <v>0.1517</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>1.3753</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1421</v>
+        <v>-1.8549</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.629</v>
+        <v>-1.0532</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5131</v>
+        <v>-0.8017</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.0158</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3823</v>
+        <v>2.5656</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0992</v>
+        <v>-0.1697</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7278</v>
+        <v>-0.0516</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.118</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5339</v>
+        <v>3.479</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5339</v>
+        <v>3.8009</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8435</v>
+        <v>2.7726</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7796</v>
+        <v>2.0531</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0638</v>
+        <v>0.7195</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3279</v>
+        <v>-0.7002</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9015</v>
+        <v>-0.4372</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5736</v>
+        <v>-0.2631</v>
       </c>
       <c r="J16" t="n">
-        <v>1.527</v>
+        <v>0.4418</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1517</v>
+        <v>0.1918</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3753</v>
+        <v>0.25</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8549</v>
+        <v>-1.1421</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0532</v>
+        <v>-0.629</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8017</v>
+        <v>-0.5131</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.0158</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5656</v>
+        <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8573</v>
+        <v>0.5724</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5324</v>
+        <v>1.0932</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3249</v>
+        <v>-0.5208</v>
       </c>
       <c r="V16" t="n">
-        <v>3.479</v>
+        <v>2.5339</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8009</v>
+        <v>2.5339</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4461</v>
+        <v>2.1668</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2909</v>
+        <v>0.7723</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8448</v>
+        <v>1.3945</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6878</v>
+        <v>-0.2773</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5151</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2029</v>
+        <v>0.3623</v>
       </c>
       <c r="J17" t="n">
-        <v>6.352</v>
+        <v>1.3626</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1487</v>
+        <v>0.5511</v>
       </c>
       <c r="L17" t="n">
-        <v>5.2032</v>
+        <v>0.8115</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6641</v>
+        <v>-1.6398</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6638</v>
+        <v>-1.1907</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0003</v>
+        <v>-0.4492</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7489</v>
+        <v>-1.0995</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828</v>
+        <v>3.1154</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1318</v>
+        <v>-0.2157</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3122</v>
+        <v>-0.1346</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8196</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6439</v>
+        <v>0.6439</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MORAL SANMARTIN</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4372</v>
+        <v>2.1571</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7463</v>
+        <v>3.6755</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3092</v>
+        <v>-1.5184</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1967</v>
+        <v>4.6878</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9433</v>
+        <v>-0.5151</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7467</v>
+        <v>5.2029</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9018</v>
+        <v>6.352</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1736</v>
+        <v>1.1487</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7282</v>
+        <v>5.2032</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7051</v>
+        <v>-1.6641</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2303</v>
+        <v>-1.6638</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4748</v>
+        <v>-0.0003</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8326</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.969</v>
+        <v>-0.4208</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5324</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4366</v>
+        <v>-0.4932</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6231</v>
+        <v>-0.6439</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>A. MORAL SANMARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4149</v>
+        <v>1.8291</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7457</v>
+        <v>3.0348</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3308</v>
+        <v>-1.2057</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3959</v>
+        <v>1.1967</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1587</v>
+        <v>1.9433</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2372</v>
+        <v>-0.7467</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0005</v>
+        <v>3.9018</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0837</v>
+        <v>3.1736</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.7282</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6047</v>
+        <v>-2.7051</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.925</v>
+        <v>-1.2303</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3204</v>
+        <v>-1.4748</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2376</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3107</v>
+        <v>-0.244</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5483</v>
+        <v>-0.3332</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6231</v>
+        <v>-0.6231</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7623</v>
+        <v>1.4469</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0992</v>
+        <v>1.6495</v>
       </c>
       <c r="F20" t="n">
-        <v>0.663</v>
+        <v>-0.2026</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2773</v>
+        <v>1.3959</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6395999999999999</v>
+        <v>0.1587</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3623</v>
+        <v>1.2372</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3626</v>
+        <v>2.0005</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5511</v>
+        <v>1.0837</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8115</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6398</v>
+        <v>-0.6047</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1907</v>
+        <v>-0.925</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4492</v>
+        <v>0.3204</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0158</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1154</v>
+        <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6202</v>
+        <v>-0.2055</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8077</v>
+        <v>0.2146</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8125</v>
+        <v>-0.4201</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6439</v>
+        <v>0.6231</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6439</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="21">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4211</v>
+        <v>0.4458</v>
       </c>
       <c r="E23" t="n">
         <v>0.1816</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2394</v>
+        <v>0.2642</v>
       </c>
       <c r="G23" t="n">
         <v>0.3865</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1486</v>
+        <v>-0.1239</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.156</v>
+        <v>0.3979</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9965000000000001</v>
+        <v>1.1888</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8404</v>
+        <v>-0.7909</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4639</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9195</v>
+        <v>-0.6776</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2021</v>
+        <v>-0.0098</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7174</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>0.6231</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8716</v>
+        <v>-1.7055</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9853</v>
+        <v>-2.1042</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1137</v>
+        <v>0.3986</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.9466</v>
+        <v>-1.8757</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.9909</v>
+        <v>2.2339</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9556</v>
+        <v>-4.1095</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4565</v>
+        <v>0.9121</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.9822</v>
+        <v>4.5082</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4743</v>
+        <v>-3.5961</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.49</v>
+        <v>-2.7878</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.0088</v>
+        <v>-2.2744</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4813</v>
+        <v>-0.5134</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1833</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9321</v>
+        <v>-4.7647</v>
       </c>
       <c r="R25" t="n">
-        <v>3.1154</v>
+        <v>3.2986</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6693</v>
+        <v>-0.2747</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4925</v>
+        <v>-0.1625</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1768</v>
+        <v>-0.1122</v>
       </c>
       <c r="V25" t="n">
-        <v>2.2224</v>
+        <v>1.9109</v>
       </c>
       <c r="W25" t="n">
         <v>1.9109</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.1615</v>
+        <v>-2.3714</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.2003</v>
+        <v>-3.3699</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0388</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8757</v>
+        <v>-4.9466</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2339</v>
+        <v>-3.9909</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.1095</v>
+        <v>-0.9556</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9121</v>
+        <v>-2.4565</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5082</v>
+        <v>-1.9822</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.5961</v>
+        <v>-0.4743</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.7878</v>
+        <v>-2.49</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.2744</v>
+        <v>-2.0088</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5134</v>
+        <v>-0.4813</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.7647</v>
+        <v>-2.9321</v>
       </c>
       <c r="R26" t="n">
-        <v>3.2986</v>
+        <v>3.1154</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7307</v>
+        <v>0.1695</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2586</v>
+        <v>0.1079</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.472</v>
+        <v>0.0616</v>
       </c>
       <c r="V26" t="n">
-        <v>1.9109</v>
+        <v>2.2224</v>
       </c>
       <c r="W26" t="n">
         <v>1.9109</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="27">
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>10.0228</v>
+        <v>11.9457</v>
       </c>
       <c r="E27" t="n">
         <v>11.6172</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.5948</v>
+        <v>0.3283999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3505999999999994</v>
+        <v>0.3505999999999991</v>
       </c>
       <c r="H27" t="n">
         <v>-2.2135</v>
@@ -2533,13 +2533,13 @@
         <v>2.564000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>16.862</v>
+        <v>16.86199999999999</v>
       </c>
       <c r="K27" t="n">
         <v>10.288</v>
       </c>
       <c r="L27" t="n">
-        <v>6.5739</v>
+        <v>6.573899999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-16.5112</v>
@@ -2560,13 +2560,13 @@
         <v>20.1584</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.8462</v>
+        <v>-1.9231</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7203999999999997</v>
+        <v>0.7203999999999998</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.5665</v>
+        <v>-2.6435</v>
       </c>
       <c r="V27" t="n">
         <v>10.7693</v>
